--- a/kronshtatsky/walls/НЗ/PGP.xlsx
+++ b/kronshtatsky/walls/НЗ/PGP.xlsx
@@ -9,14 +9,16 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10416"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16056" windowHeight="8796" firstSheet="1" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="2" r:id="rId1"/>
     <sheet name="ПГП" sheetId="1" r:id="rId2"/>
-    <sheet name="1 эт" sheetId="3" r:id="rId3"/>
-    <sheet name="2 эт" sheetId="5" r:id="rId4"/>
-    <sheet name="3 эт" sheetId="6" r:id="rId5"/>
+    <sheet name="ПГП-НЗ" sheetId="8" r:id="rId3"/>
+    <sheet name="4.1-пом" sheetId="10" r:id="rId4"/>
+    <sheet name="1 эт" sheetId="3" r:id="rId5"/>
+    <sheet name="2 эт" sheetId="5" r:id="rId6"/>
+    <sheet name="3 эт" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -28,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="143">
   <si>
     <t>Ведомость работ и используемых материалов</t>
   </si>
@@ -271,6 +273,192 @@
   </si>
   <si>
     <t>1.21 Помещение для приготовления дезинфицирующих растворов</t>
+  </si>
+  <si>
+    <t>1-3 этаж</t>
+  </si>
+  <si>
+    <t>Кладка внутренних стен из блоков ячеистого бетона без устройства перемычек, включая армирование, устройство примыканий</t>
+  </si>
+  <si>
+    <t>м3</t>
+  </si>
+  <si>
+    <t>1.05</t>
+  </si>
+  <si>
+    <t>1.06</t>
+  </si>
+  <si>
+    <t>1.08</t>
+  </si>
+  <si>
+    <t>1.26</t>
+  </si>
+  <si>
+    <t>1.29</t>
+  </si>
+  <si>
+    <t>1.30</t>
+  </si>
+  <si>
+    <t>1.10</t>
+  </si>
+  <si>
+    <t>1.09</t>
+  </si>
+  <si>
+    <t>1.27</t>
+  </si>
+  <si>
+    <t>1.39</t>
+  </si>
+  <si>
+    <t>1.38</t>
+  </si>
+  <si>
+    <t>1.41</t>
+  </si>
+  <si>
+    <t>1.82</t>
+  </si>
+  <si>
+    <t>1.31</t>
+  </si>
+  <si>
+    <t>1.63</t>
+  </si>
+  <si>
+    <t>1.77</t>
+  </si>
+  <si>
+    <t>1.78</t>
+  </si>
+  <si>
+    <t>1.61</t>
+  </si>
+  <si>
+    <t>1.59</t>
+  </si>
+  <si>
+    <t>1.62</t>
+  </si>
+  <si>
+    <t>Этаж</t>
+  </si>
+  <si>
+    <t>2.21</t>
+  </si>
+  <si>
+    <t>2.01</t>
+  </si>
+  <si>
+    <t>2.02</t>
+  </si>
+  <si>
+    <t>2.03</t>
+  </si>
+  <si>
+    <t>2.23</t>
+  </si>
+  <si>
+    <t>2.58</t>
+  </si>
+  <si>
+    <t>1.04</t>
+  </si>
+  <si>
+    <t>2.28</t>
+  </si>
+  <si>
+    <t>2.33</t>
+  </si>
+  <si>
+    <t>2.19</t>
+  </si>
+  <si>
+    <t>2.30</t>
+  </si>
+  <si>
+    <t>2.04</t>
+  </si>
+  <si>
+    <t>2.05</t>
+  </si>
+  <si>
+    <t>2.06</t>
+  </si>
+  <si>
+    <t>2.08</t>
+  </si>
+  <si>
+    <t>2.07</t>
+  </si>
+  <si>
+    <t>2.50</t>
+  </si>
+  <si>
+    <t>2.49</t>
+  </si>
+  <si>
+    <t>2.51</t>
+  </si>
+  <si>
+    <t>2,56</t>
+  </si>
+  <si>
+    <t>2.47</t>
+  </si>
+  <si>
+    <t>3.01</t>
+  </si>
+  <si>
+    <t>3.02</t>
+  </si>
+  <si>
+    <t>3.03</t>
+  </si>
+  <si>
+    <t>3.04</t>
+  </si>
+  <si>
+    <t>3.05</t>
+  </si>
+  <si>
+    <t>3.45</t>
+  </si>
+  <si>
+    <t>3,15</t>
+  </si>
+  <si>
+    <t>3.18</t>
+  </si>
+  <si>
+    <t>3.19</t>
+  </si>
+  <si>
+    <t>3.12</t>
+  </si>
+  <si>
+    <t>3.22</t>
+  </si>
+  <si>
+    <t>3.41</t>
+  </si>
+  <si>
+    <t>3.35</t>
+  </si>
+  <si>
+    <t>3.33</t>
+  </si>
+  <si>
+    <t>3.42</t>
+  </si>
+  <si>
+    <t>1.75</t>
+  </si>
+  <si>
+    <t>Пом.</t>
   </si>
 </sst>
 </file>
@@ -280,7 +468,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -322,6 +510,8 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="ГОСТ тип А"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
@@ -330,8 +520,16 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="4" tint="-0.249977111117893"/>
+      <name val="ГОСТ тип А"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -350,8 +548,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="15">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -527,11 +731,148 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -646,11 +987,357 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="35">
+  <dxfs count="44">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="4" tint="-0.249977111117893"/>
+        <name val="ГОСТ тип А"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="4" tint="-0.249977111117893"/>
+        <name val="ГОСТ тип А"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="4" tint="-0.249977111117893"/>
+        <name val="ГОСТ тип А"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color theme="4" tint="-0.249977111117893"/>
+        <name val="ГОСТ тип А"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color theme="4" tint="-0.249977111117893"/>
+        <name val="ГОСТ тип А"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="ГОСТ тип А"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -1753,19 +2440,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Таблица1" displayName="Таблица1" ref="A2:G60" totalsRowShown="0" headerRowDxfId="34" headerRowBorderDxfId="33" tableBorderDxfId="32" totalsRowBorderDxfId="31">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Таблица1" displayName="Таблица1" ref="A2:G60" totalsRowShown="0" headerRowDxfId="43" headerRowBorderDxfId="42" tableBorderDxfId="41" totalsRowBorderDxfId="40">
   <autoFilter ref="A2:G60"/>
   <sortState ref="A3:F60">
     <sortCondition ref="A2:A60"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" name="Помещения" dataDxfId="30"/>
-    <tableColumn id="2" name="Тип" dataDxfId="29"/>
-    <tableColumn id="3" name="Ед. изм." dataDxfId="28"/>
-    <tableColumn id="4" name="Объем." dataDxfId="27"/>
-    <tableColumn id="7" name="ВПГП" dataDxfId="26"/>
-    <tableColumn id="8" name="ПГП" dataDxfId="25"/>
-    <tableColumn id="9" name="Разница" dataDxfId="24">
+    <tableColumn id="1" name="Помещения" dataDxfId="39"/>
+    <tableColumn id="2" name="Тип" dataDxfId="38"/>
+    <tableColumn id="3" name="Ед. изм." dataDxfId="37"/>
+    <tableColumn id="4" name="Объем." dataDxfId="36"/>
+    <tableColumn id="7" name="ВПГП" dataDxfId="35"/>
+    <tableColumn id="8" name="ПГП" dataDxfId="34"/>
+    <tableColumn id="9" name="Разница" dataDxfId="33">
       <calculatedColumnFormula>(Таблица1[[#This Row],[ВПГП]]+Таблица1[[#This Row],[ПГП]])-Таблица1[[#This Row],[Объем.]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1774,17 +2461,33 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Таблица13" displayName="Таблица13" ref="A2:E19" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22" tableBorderDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Таблица16" displayName="Таблица16" ref="A5:D27" totalsRowShown="0" headerRowDxfId="8" dataDxfId="4" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
+  <autoFilter ref="A5:D27"/>
+  <sortState ref="B3:G60">
+    <sortCondition ref="B2:B60"/>
+  </sortState>
+  <tableColumns count="4">
+    <tableColumn id="5" name="Этаж" dataDxfId="3"/>
+    <tableColumn id="1" name="Пом." dataDxfId="2"/>
+    <tableColumn id="3" name="Ед. изм." dataDxfId="1"/>
+    <tableColumn id="4" name="Объем." dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Таблица13" displayName="Таблица13" ref="A2:E19" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31" tableBorderDxfId="30">
   <autoFilter ref="A2:E19"/>
   <sortState ref="A3:F60">
     <sortCondition ref="A2:A60"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="1" name="Помещения" dataDxfId="20"/>
-    <tableColumn id="3" name="Ед. изм." dataDxfId="19"/>
-    <tableColumn id="7" name="ВПГП" dataDxfId="18"/>
-    <tableColumn id="8" name="ПГП" dataDxfId="17"/>
-    <tableColumn id="9" name="Итог:" dataDxfId="16">
+    <tableColumn id="1" name="Помещения" dataDxfId="29"/>
+    <tableColumn id="3" name="Ед. изм." dataDxfId="28"/>
+    <tableColumn id="7" name="ВПГП" dataDxfId="27"/>
+    <tableColumn id="8" name="ПГП" dataDxfId="26"/>
+    <tableColumn id="9" name="Итог:" dataDxfId="25">
       <calculatedColumnFormula>Таблица13[[#This Row],[ПГП]]+Таблица13[[#This Row],[ВПГП]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1792,18 +2495,18 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Таблица134" displayName="Таблица134" ref="A2:E22" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14" tableBorderDxfId="13">
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Таблица134" displayName="Таблица134" ref="A2:E22" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23" tableBorderDxfId="22">
   <autoFilter ref="A2:E22"/>
   <sortState ref="A3:F60">
     <sortCondition ref="A2:A60"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="1" name="Помещения" dataDxfId="12"/>
-    <tableColumn id="3" name="Ед. изм." dataDxfId="11"/>
-    <tableColumn id="7" name="АС влаго" dataDxfId="10"/>
-    <tableColumn id="8" name="ПГП" dataDxfId="9"/>
-    <tableColumn id="9" name="Итог:" dataDxfId="8">
+    <tableColumn id="1" name="Помещения" dataDxfId="21"/>
+    <tableColumn id="3" name="Ед. изм." dataDxfId="20"/>
+    <tableColumn id="7" name="АС влаго" dataDxfId="19"/>
+    <tableColumn id="8" name="ПГП" dataDxfId="18"/>
+    <tableColumn id="9" name="Итог:" dataDxfId="17">
       <calculatedColumnFormula>Таблица134[[#This Row],[ПГП]]+Таблица134[[#This Row],[АС влаго]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1811,18 +2514,18 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица1345" displayName="Таблица1345" ref="A2:E18" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6" tableBorderDxfId="5">
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица1345" displayName="Таблица1345" ref="A2:E18" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15" tableBorderDxfId="14">
   <autoFilter ref="A2:E18"/>
   <sortState ref="A3:F60">
     <sortCondition ref="A2:A60"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="1" name="Помещения" dataDxfId="4"/>
-    <tableColumn id="3" name="Ед. изм." dataDxfId="3"/>
-    <tableColumn id="7" name="АС влаго" dataDxfId="2"/>
-    <tableColumn id="8" name="ПГП" dataDxfId="1"/>
-    <tableColumn id="9" name="Итог:" dataDxfId="0">
+    <tableColumn id="1" name="Помещения" dataDxfId="13"/>
+    <tableColumn id="3" name="Ед. изм." dataDxfId="12"/>
+    <tableColumn id="7" name="АС влаго" dataDxfId="11"/>
+    <tableColumn id="8" name="ПГП" dataDxfId="10"/>
+    <tableColumn id="9" name="Итог:" dataDxfId="9">
       <calculatedColumnFormula>Таблица1345[[#This Row],[ПГП]]+Таблица1345[[#This Row],[АС влаго]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3521,6 +4224,1074 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.6640625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="37.88671875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" style="5" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="9.21875" style="5" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="4"/>
+    </row>
+    <row r="2" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A3" s="7">
+        <v>1</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="49">
+        <f>'1 эт'!E20+'2 эт'!E23+'3 эт'!E19+1005.14</f>
+        <v>2519.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FFFFC000"/>
+  </sheetPr>
+  <dimension ref="A1:N27"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="50"/>
+    <col min="2" max="2" width="9.33203125" style="50" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" style="50" customWidth="1"/>
+    <col min="4" max="4" width="8.88671875" style="50"/>
+    <col min="5" max="5" width="6.77734375" style="50" customWidth="1"/>
+    <col min="6" max="6" width="7.33203125" style="50" customWidth="1"/>
+    <col min="7" max="9" width="8.88671875" style="50"/>
+    <col min="10" max="10" width="6.5546875" style="50" customWidth="1"/>
+    <col min="11" max="11" width="7.44140625" style="50" customWidth="1"/>
+    <col min="12" max="12" width="7.5546875" style="50" customWidth="1"/>
+    <col min="13" max="13" width="9.6640625" style="50" customWidth="1"/>
+    <col min="14" max="16384" width="8.88671875" style="50"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+    </row>
+    <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="71" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="73"/>
+      <c r="K2" s="70" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" s="70"/>
+      <c r="M2" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="N2" s="23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="64.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="7">
+        <v>1</v>
+      </c>
+      <c r="B3" s="74" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="76"/>
+      <c r="K3" s="70" t="s">
+        <v>81</v>
+      </c>
+      <c r="L3" s="70"/>
+      <c r="M3" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="N3" s="23">
+        <f>N22+I27+D27</f>
+        <v>362.59000000000003</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="77"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="77"/>
+      <c r="M4" s="77"/>
+      <c r="N4" s="77"/>
+    </row>
+    <row r="5" spans="1:14" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="54" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="55" t="s">
+        <v>142</v>
+      </c>
+      <c r="C5" s="54" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="54" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="78"/>
+      <c r="F5" s="60" t="s">
+        <v>104</v>
+      </c>
+      <c r="G5" s="61" t="s">
+        <v>142</v>
+      </c>
+      <c r="H5" s="62" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5" s="63" t="s">
+        <v>67</v>
+      </c>
+      <c r="J5" s="68"/>
+      <c r="K5" s="60" t="s">
+        <v>104</v>
+      </c>
+      <c r="L5" s="61" t="s">
+        <v>142</v>
+      </c>
+      <c r="M5" s="62" t="s">
+        <v>4</v>
+      </c>
+      <c r="N5" s="63" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="56">
+        <v>1</v>
+      </c>
+      <c r="B6" s="57" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="D6" s="51">
+        <v>6.9</v>
+      </c>
+      <c r="E6" s="78"/>
+      <c r="F6" s="64">
+        <v>2</v>
+      </c>
+      <c r="G6" s="59" t="s">
+        <v>105</v>
+      </c>
+      <c r="H6" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="I6" s="65">
+        <v>4.62</v>
+      </c>
+      <c r="J6" s="68"/>
+      <c r="K6" s="66">
+        <v>3</v>
+      </c>
+      <c r="L6" s="58" t="s">
+        <v>126</v>
+      </c>
+      <c r="M6" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="N6" s="67">
+        <v>11.77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="56">
+        <v>1</v>
+      </c>
+      <c r="B7" s="57" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="D7" s="51">
+        <v>5.76</v>
+      </c>
+      <c r="E7" s="78"/>
+      <c r="F7" s="66">
+        <v>2</v>
+      </c>
+      <c r="G7" s="58" t="s">
+        <v>106</v>
+      </c>
+      <c r="H7" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="I7" s="67">
+        <v>10.41</v>
+      </c>
+      <c r="J7" s="68"/>
+      <c r="K7" s="64">
+        <v>3</v>
+      </c>
+      <c r="L7" s="59" t="s">
+        <v>127</v>
+      </c>
+      <c r="M7" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="N7" s="65">
+        <v>9.18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="56">
+        <v>1</v>
+      </c>
+      <c r="B8" s="57" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8" s="51">
+        <v>7.86</v>
+      </c>
+      <c r="E8" s="78"/>
+      <c r="F8" s="64">
+        <v>2</v>
+      </c>
+      <c r="G8" s="59" t="s">
+        <v>107</v>
+      </c>
+      <c r="H8" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="I8" s="65">
+        <v>9</v>
+      </c>
+      <c r="J8" s="68"/>
+      <c r="K8" s="66">
+        <v>3</v>
+      </c>
+      <c r="L8" s="58" t="s">
+        <v>128</v>
+      </c>
+      <c r="M8" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="N8" s="67">
+        <v>5.44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="56">
+        <v>1</v>
+      </c>
+      <c r="B9" s="57" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" s="51">
+        <v>8.89</v>
+      </c>
+      <c r="E9" s="78"/>
+      <c r="F9" s="66">
+        <v>2</v>
+      </c>
+      <c r="G9" s="58" t="s">
+        <v>108</v>
+      </c>
+      <c r="H9" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="I9" s="67">
+        <v>6.96</v>
+      </c>
+      <c r="J9" s="68"/>
+      <c r="K9" s="64">
+        <v>3</v>
+      </c>
+      <c r="L9" s="59" t="s">
+        <v>129</v>
+      </c>
+      <c r="M9" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="N9" s="65">
+        <v>3.78</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="56">
+        <v>1</v>
+      </c>
+      <c r="B10" s="57" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10" s="51">
+        <v>1.52</v>
+      </c>
+      <c r="E10" s="78"/>
+      <c r="F10" s="64">
+        <v>2</v>
+      </c>
+      <c r="G10" s="59" t="s">
+        <v>109</v>
+      </c>
+      <c r="H10" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="I10" s="65">
+        <v>5.79</v>
+      </c>
+      <c r="J10" s="68"/>
+      <c r="K10" s="66">
+        <v>3</v>
+      </c>
+      <c r="L10" s="58" t="s">
+        <v>130</v>
+      </c>
+      <c r="M10" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="N10" s="67">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="56">
+        <v>1</v>
+      </c>
+      <c r="B11" s="57" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="D11" s="51">
+        <v>9.84</v>
+      </c>
+      <c r="E11" s="78"/>
+      <c r="F11" s="66">
+        <v>2</v>
+      </c>
+      <c r="G11" s="58" t="s">
+        <v>110</v>
+      </c>
+      <c r="H11" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="I11" s="67">
+        <v>1.2</v>
+      </c>
+      <c r="J11" s="68"/>
+      <c r="K11" s="64">
+        <v>3</v>
+      </c>
+      <c r="L11" s="59" t="s">
+        <v>131</v>
+      </c>
+      <c r="M11" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="N11" s="65">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="56">
+        <v>1</v>
+      </c>
+      <c r="B12" s="57" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" s="51">
+        <v>3.78</v>
+      </c>
+      <c r="E12" s="78"/>
+      <c r="F12" s="64">
+        <v>2</v>
+      </c>
+      <c r="G12" s="59" t="s">
+        <v>111</v>
+      </c>
+      <c r="H12" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="I12" s="65">
+        <v>3.96</v>
+      </c>
+      <c r="J12" s="68"/>
+      <c r="K12" s="66">
+        <v>3</v>
+      </c>
+      <c r="L12" s="58" t="s">
+        <v>132</v>
+      </c>
+      <c r="M12" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="N12" s="67">
+        <v>5.82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="56">
+        <v>1</v>
+      </c>
+      <c r="B13" s="57" t="s">
+        <v>91</v>
+      </c>
+      <c r="C13" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="D13" s="51">
+        <v>1.95</v>
+      </c>
+      <c r="E13" s="78"/>
+      <c r="F13" s="66">
+        <v>2</v>
+      </c>
+      <c r="G13" s="58" t="s">
+        <v>112</v>
+      </c>
+      <c r="H13" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="I13" s="67">
+        <v>1.75</v>
+      </c>
+      <c r="J13" s="68"/>
+      <c r="K13" s="64">
+        <v>3</v>
+      </c>
+      <c r="L13" s="59" t="s">
+        <v>133</v>
+      </c>
+      <c r="M13" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="N13" s="65">
+        <v>4.3099999999999996</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="56">
+        <v>1</v>
+      </c>
+      <c r="B14" s="57" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="D14" s="51">
+        <v>1.2</v>
+      </c>
+      <c r="E14" s="78"/>
+      <c r="F14" s="64">
+        <v>2</v>
+      </c>
+      <c r="G14" s="59" t="s">
+        <v>113</v>
+      </c>
+      <c r="H14" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="I14" s="65">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="J14" s="68"/>
+      <c r="K14" s="66">
+        <v>3</v>
+      </c>
+      <c r="L14" s="58" t="s">
+        <v>134</v>
+      </c>
+      <c r="M14" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="N14" s="67">
+        <f>10.04+2.57</f>
+        <v>12.61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="56">
+        <v>1</v>
+      </c>
+      <c r="B15" s="57" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="D15" s="51">
+        <v>12.5</v>
+      </c>
+      <c r="E15" s="78"/>
+      <c r="F15" s="66">
+        <v>2</v>
+      </c>
+      <c r="G15" s="58" t="s">
+        <v>114</v>
+      </c>
+      <c r="H15" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="I15" s="67">
+        <v>5.56</v>
+      </c>
+      <c r="J15" s="68"/>
+      <c r="K15" s="64">
+        <v>3</v>
+      </c>
+      <c r="L15" s="59" t="s">
+        <v>135</v>
+      </c>
+      <c r="M15" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="N15" s="65">
+        <v>10.15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="56">
+        <v>1</v>
+      </c>
+      <c r="B16" s="57" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" s="51">
+        <v>4.08</v>
+      </c>
+      <c r="E16" s="78"/>
+      <c r="F16" s="64">
+        <v>2</v>
+      </c>
+      <c r="G16" s="59" t="s">
+        <v>115</v>
+      </c>
+      <c r="H16" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="I16" s="65">
+        <v>15.79</v>
+      </c>
+      <c r="J16" s="68"/>
+      <c r="K16" s="66">
+        <v>3</v>
+      </c>
+      <c r="L16" s="58" t="s">
+        <v>136</v>
+      </c>
+      <c r="M16" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="N16" s="67">
+        <v>4.16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="56">
+        <v>1</v>
+      </c>
+      <c r="B17" s="57" t="s">
+        <v>94</v>
+      </c>
+      <c r="C17" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" s="51">
+        <v>12.1</v>
+      </c>
+      <c r="E17" s="78"/>
+      <c r="F17" s="66">
+        <v>2</v>
+      </c>
+      <c r="G17" s="58" t="s">
+        <v>116</v>
+      </c>
+      <c r="H17" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="I17" s="67">
+        <v>1.76</v>
+      </c>
+      <c r="J17" s="68"/>
+      <c r="K17" s="64">
+        <v>3</v>
+      </c>
+      <c r="L17" s="59" t="s">
+        <v>137</v>
+      </c>
+      <c r="M17" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="N17" s="65">
+        <v>4.51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="56">
+        <v>1</v>
+      </c>
+      <c r="B18" s="57" t="s">
+        <v>96</v>
+      </c>
+      <c r="C18" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="D18" s="51">
+        <f>0.42+1.98</f>
+        <v>2.4</v>
+      </c>
+      <c r="E18" s="78"/>
+      <c r="F18" s="64">
+        <v>2</v>
+      </c>
+      <c r="G18" s="59" t="s">
+        <v>117</v>
+      </c>
+      <c r="H18" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="I18" s="65">
+        <v>7.48</v>
+      </c>
+      <c r="J18" s="68"/>
+      <c r="K18" s="66">
+        <v>3</v>
+      </c>
+      <c r="L18" s="58" t="s">
+        <v>138</v>
+      </c>
+      <c r="M18" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="N18" s="67">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="56">
+        <v>1</v>
+      </c>
+      <c r="B19" s="57" t="s">
+        <v>97</v>
+      </c>
+      <c r="C19" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19" s="51">
+        <v>21.81</v>
+      </c>
+      <c r="E19" s="78"/>
+      <c r="F19" s="66">
+        <v>2</v>
+      </c>
+      <c r="G19" s="58" t="s">
+        <v>118</v>
+      </c>
+      <c r="H19" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="I19" s="67">
+        <v>1.88</v>
+      </c>
+      <c r="J19" s="68"/>
+      <c r="K19" s="64">
+        <v>3</v>
+      </c>
+      <c r="L19" s="59" t="s">
+        <v>139</v>
+      </c>
+      <c r="M19" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="N19" s="65">
+        <v>11.94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="56">
+        <v>1</v>
+      </c>
+      <c r="B20" s="57" t="s">
+        <v>98</v>
+      </c>
+      <c r="C20" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" s="51">
+        <v>1.59</v>
+      </c>
+      <c r="E20" s="78"/>
+      <c r="F20" s="64">
+        <v>2</v>
+      </c>
+      <c r="G20" s="59" t="s">
+        <v>119</v>
+      </c>
+      <c r="H20" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="I20" s="65">
+        <v>12.78</v>
+      </c>
+      <c r="J20" s="68"/>
+      <c r="K20" s="66">
+        <v>3</v>
+      </c>
+      <c r="L20" s="58" t="s">
+        <v>140</v>
+      </c>
+      <c r="M20" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="N20" s="67">
+        <v>7.27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="56">
+        <v>1</v>
+      </c>
+      <c r="B21" s="57" t="s">
+        <v>141</v>
+      </c>
+      <c r="C21" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" s="51">
+        <v>2.4</v>
+      </c>
+      <c r="E21" s="78"/>
+      <c r="F21" s="66">
+        <v>2</v>
+      </c>
+      <c r="G21" s="58" t="s">
+        <v>120</v>
+      </c>
+      <c r="H21" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="I21" s="67">
+        <v>5.38</v>
+      </c>
+      <c r="J21" s="68"/>
+      <c r="K21" s="64">
+        <v>3</v>
+      </c>
+      <c r="L21" s="59" t="s">
+        <v>135</v>
+      </c>
+      <c r="M21" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="N21" s="65">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="56">
+        <v>1</v>
+      </c>
+      <c r="B22" s="57" t="s">
+        <v>99</v>
+      </c>
+      <c r="C22" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="D22" s="51">
+        <v>4.53</v>
+      </c>
+      <c r="E22" s="78"/>
+      <c r="F22" s="64">
+        <v>2</v>
+      </c>
+      <c r="G22" s="59" t="s">
+        <v>121</v>
+      </c>
+      <c r="H22" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="I22" s="65">
+        <v>1.36</v>
+      </c>
+      <c r="J22" s="68"/>
+      <c r="L22" s="59" t="s">
+        <v>71</v>
+      </c>
+      <c r="M22" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="N22" s="50">
+        <f>SUM(N6:N21)</f>
+        <v>112.27000000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="56">
+        <v>1</v>
+      </c>
+      <c r="B23" s="57" t="s">
+        <v>100</v>
+      </c>
+      <c r="C23" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="D23" s="51">
+        <v>10.92</v>
+      </c>
+      <c r="E23" s="78"/>
+      <c r="F23" s="66">
+        <v>2</v>
+      </c>
+      <c r="G23" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="H23" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="I23" s="67">
+        <v>8.0399999999999991</v>
+      </c>
+      <c r="J23" s="68"/>
+      <c r="K23" s="68"/>
+      <c r="L23" s="68"/>
+      <c r="M23" s="68"/>
+      <c r="N23" s="68"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="56">
+        <v>1</v>
+      </c>
+      <c r="B24" s="57" t="s">
+        <v>101</v>
+      </c>
+      <c r="C24" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24" s="51">
+        <v>2.6</v>
+      </c>
+      <c r="E24" s="78"/>
+      <c r="F24" s="64">
+        <v>2</v>
+      </c>
+      <c r="G24" s="59" t="s">
+        <v>123</v>
+      </c>
+      <c r="H24" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="I24" s="65">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="J24" s="68"/>
+      <c r="K24" s="68"/>
+      <c r="L24" s="68"/>
+      <c r="M24" s="68"/>
+      <c r="N24" s="68"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="56">
+        <v>1</v>
+      </c>
+      <c r="B25" s="57" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="D25" s="51">
+        <v>1.77</v>
+      </c>
+      <c r="E25" s="78"/>
+      <c r="F25" s="66">
+        <v>2</v>
+      </c>
+      <c r="G25" s="58" t="s">
+        <v>124</v>
+      </c>
+      <c r="H25" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="I25" s="67">
+        <v>6.51</v>
+      </c>
+      <c r="J25" s="68"/>
+      <c r="K25" s="68"/>
+      <c r="L25" s="68"/>
+      <c r="M25" s="68"/>
+      <c r="N25" s="68"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="56">
+        <v>1</v>
+      </c>
+      <c r="B26" s="57" t="s">
+        <v>103</v>
+      </c>
+      <c r="C26" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="D26" s="51">
+        <v>4.3</v>
+      </c>
+      <c r="E26" s="78"/>
+      <c r="F26" s="64">
+        <v>2</v>
+      </c>
+      <c r="G26" s="59" t="s">
+        <v>125</v>
+      </c>
+      <c r="H26" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="I26" s="65">
+        <v>2.72</v>
+      </c>
+      <c r="J26" s="68"/>
+      <c r="K26" s="68"/>
+      <c r="L26" s="68"/>
+      <c r="M26" s="68"/>
+      <c r="N26" s="68"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="56"/>
+      <c r="B27" s="57" t="s">
+        <v>71</v>
+      </c>
+      <c r="C27" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="D27" s="51">
+        <f>SUM(D6:D26)</f>
+        <v>128.70000000000002</v>
+      </c>
+      <c r="E27" s="78"/>
+      <c r="G27" s="59" t="s">
+        <v>71</v>
+      </c>
+      <c r="H27" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="I27" s="50">
+        <f>SUM(I6:I26)</f>
+        <v>121.62</v>
+      </c>
+      <c r="J27" s="68"/>
+      <c r="K27" s="68"/>
+      <c r="L27" s="68"/>
+      <c r="M27" s="68"/>
+      <c r="N27" s="68"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A4:N4"/>
+    <mergeCell ref="J5:J27"/>
+    <mergeCell ref="E5:E27"/>
+    <mergeCell ref="K23:N27"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="B2:J2"/>
+    <mergeCell ref="B3:J3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
@@ -3860,7 +5631,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
@@ -4252,7 +6023,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>

--- a/kronshtatsky/walls/НЗ/PGP.xlsx
+++ b/kronshtatsky/walls/НЗ/PGP.xlsx
@@ -20,7 +20,7 @@
     <sheet name="2 эт" sheetId="5" r:id="rId6"/>
     <sheet name="3 эт" sheetId="6" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="152511" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1041,13 +1041,19 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1068,276 +1074,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="44">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="4" tint="-0.249977111117893"/>
-        <name val="ГОСТ тип А"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="4" tint="-0.249977111117893"/>
-        <name val="ГОСТ тип А"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="4" tint="-0.249977111117893"/>
-        <name val="ГОСТ тип А"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <color theme="4" tint="-0.249977111117893"/>
-        <name val="ГОСТ тип А"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <color theme="4" tint="-0.249977111117893"/>
-        <name val="ГОСТ тип А"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="ГОСТ тип А"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -2091,6 +1832,265 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="14"/>
+        <color theme="4" tint="-0.249977111117893"/>
+        <name val="ГОСТ тип А"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="4" tint="-0.249977111117893"/>
+        <name val="ГОСТ тип А"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="4" tint="-0.249977111117893"/>
+        <name val="ГОСТ тип А"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color theme="4" tint="-0.249977111117893"/>
+        <name val="ГОСТ тип А"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color theme="4" tint="-0.249977111117893"/>
+        <name val="ГОСТ тип А"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="ГОСТ тип А"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
         <color rgb="FF000000"/>
         <name val="ГОСТ тип А"/>
         <scheme val="none"/>
@@ -2461,33 +2461,33 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Таблица16" displayName="Таблица16" ref="A5:D27" totalsRowShown="0" headerRowDxfId="8" dataDxfId="4" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Таблица16" displayName="Таблица16" ref="A5:D27" totalsRowShown="0" headerRowDxfId="32" dataDxfId="30" headerRowBorderDxfId="31" tableBorderDxfId="29" totalsRowBorderDxfId="28">
   <autoFilter ref="A5:D27"/>
   <sortState ref="B3:G60">
     <sortCondition ref="B2:B60"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="5" name="Этаж" dataDxfId="3"/>
-    <tableColumn id="1" name="Пом." dataDxfId="2"/>
-    <tableColumn id="3" name="Ед. изм." dataDxfId="1"/>
-    <tableColumn id="4" name="Объем." dataDxfId="0"/>
+    <tableColumn id="5" name="Этаж" dataDxfId="27"/>
+    <tableColumn id="1" name="Пом." dataDxfId="26"/>
+    <tableColumn id="3" name="Ед. изм." dataDxfId="25"/>
+    <tableColumn id="4" name="Объем." dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Таблица13" displayName="Таблица13" ref="A2:E19" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31" tableBorderDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Таблица13" displayName="Таблица13" ref="A2:E19" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22" tableBorderDxfId="21">
   <autoFilter ref="A2:E19"/>
   <sortState ref="A3:F60">
     <sortCondition ref="A2:A60"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="1" name="Помещения" dataDxfId="29"/>
-    <tableColumn id="3" name="Ед. изм." dataDxfId="28"/>
-    <tableColumn id="7" name="ВПГП" dataDxfId="27"/>
-    <tableColumn id="8" name="ПГП" dataDxfId="26"/>
-    <tableColumn id="9" name="Итог:" dataDxfId="25">
+    <tableColumn id="1" name="Помещения" dataDxfId="20"/>
+    <tableColumn id="3" name="Ед. изм." dataDxfId="19"/>
+    <tableColumn id="7" name="ВПГП" dataDxfId="18"/>
+    <tableColumn id="8" name="ПГП" dataDxfId="17"/>
+    <tableColumn id="9" name="Итог:" dataDxfId="16">
       <calculatedColumnFormula>Таблица13[[#This Row],[ПГП]]+Таблица13[[#This Row],[ВПГП]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2496,17 +2496,17 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Таблица134" displayName="Таблица134" ref="A2:E22" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23" tableBorderDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Таблица134" displayName="Таблица134" ref="A2:E22" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14" tableBorderDxfId="13">
   <autoFilter ref="A2:E22"/>
   <sortState ref="A3:F60">
     <sortCondition ref="A2:A60"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="1" name="Помещения" dataDxfId="21"/>
-    <tableColumn id="3" name="Ед. изм." dataDxfId="20"/>
-    <tableColumn id="7" name="АС влаго" dataDxfId="19"/>
-    <tableColumn id="8" name="ПГП" dataDxfId="18"/>
-    <tableColumn id="9" name="Итог:" dataDxfId="17">
+    <tableColumn id="1" name="Помещения" dataDxfId="12"/>
+    <tableColumn id="3" name="Ед. изм." dataDxfId="11"/>
+    <tableColumn id="7" name="АС влаго" dataDxfId="10"/>
+    <tableColumn id="8" name="ПГП" dataDxfId="9"/>
+    <tableColumn id="9" name="Итог:" dataDxfId="8">
       <calculatedColumnFormula>Таблица134[[#This Row],[ПГП]]+Таблица134[[#This Row],[АС влаго]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2515,17 +2515,17 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица1345" displayName="Таблица1345" ref="A2:E18" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15" tableBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица1345" displayName="Таблица1345" ref="A2:E18" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6" tableBorderDxfId="5">
   <autoFilter ref="A2:E18"/>
   <sortState ref="A3:F60">
     <sortCondition ref="A2:A60"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="1" name="Помещения" dataDxfId="13"/>
-    <tableColumn id="3" name="Ед. изм." dataDxfId="12"/>
-    <tableColumn id="7" name="АС влаго" dataDxfId="11"/>
-    <tableColumn id="8" name="ПГП" dataDxfId="10"/>
-    <tableColumn id="9" name="Итог:" dataDxfId="9">
+    <tableColumn id="1" name="Помещения" dataDxfId="4"/>
+    <tableColumn id="3" name="Ед. изм." dataDxfId="3"/>
+    <tableColumn id="7" name="АС влаго" dataDxfId="2"/>
+    <tableColumn id="8" name="ПГП" dataDxfId="1"/>
+    <tableColumn id="9" name="Итог:" dataDxfId="0">
       <calculatedColumnFormula>Таблица1345[[#This Row],[ПГП]]+Таблица1345[[#This Row],[АС влаго]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4307,42 +4307,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
-      <c r="I1" s="69"/>
-      <c r="J1" s="69"/>
-      <c r="K1" s="69"/>
-      <c r="L1" s="69"/>
-      <c r="M1" s="69"/>
-      <c r="N1" s="69"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="72"/>
     </row>
     <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="71" t="s">
+      <c r="B2" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="70" t="s">
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="74"/>
+      <c r="I2" s="74"/>
+      <c r="J2" s="75"/>
+      <c r="K2" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="70"/>
+      <c r="L2" s="71"/>
       <c r="M2" s="23" t="s">
         <v>4</v>
       </c>
@@ -4354,21 +4354,21 @@
       <c r="A3" s="7">
         <v>1</v>
       </c>
-      <c r="B3" s="74" t="s">
+      <c r="B3" s="76" t="s">
         <v>82</v>
       </c>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="76"/>
-      <c r="K3" s="70" t="s">
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="78"/>
+      <c r="K3" s="71" t="s">
         <v>81</v>
       </c>
-      <c r="L3" s="70"/>
+      <c r="L3" s="71"/>
       <c r="M3" s="23" t="s">
         <v>83</v>
       </c>
@@ -4378,20 +4378,20 @@
       </c>
     </row>
     <row r="4" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="77"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
-      <c r="K4" s="77"/>
-      <c r="L4" s="77"/>
-      <c r="M4" s="77"/>
-      <c r="N4" s="77"/>
+      <c r="A4" s="68"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="68"/>
+      <c r="M4" s="68"/>
+      <c r="N4" s="68"/>
     </row>
     <row r="5" spans="1:14" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="54" t="s">
@@ -4406,7 +4406,7 @@
       <c r="D5" s="54" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="78"/>
+      <c r="E5" s="70"/>
       <c r="F5" s="60" t="s">
         <v>104</v>
       </c>
@@ -4419,7 +4419,7 @@
       <c r="I5" s="63" t="s">
         <v>67</v>
       </c>
-      <c r="J5" s="68"/>
+      <c r="J5" s="69"/>
       <c r="K5" s="60" t="s">
         <v>104</v>
       </c>
@@ -4446,7 +4446,7 @@
       <c r="D6" s="51">
         <v>6.9</v>
       </c>
-      <c r="E6" s="78"/>
+      <c r="E6" s="70"/>
       <c r="F6" s="64">
         <v>2</v>
       </c>
@@ -4459,7 +4459,7 @@
       <c r="I6" s="65">
         <v>4.62</v>
       </c>
-      <c r="J6" s="68"/>
+      <c r="J6" s="69"/>
       <c r="K6" s="66">
         <v>3</v>
       </c>
@@ -4486,7 +4486,7 @@
       <c r="D7" s="51">
         <v>5.76</v>
       </c>
-      <c r="E7" s="78"/>
+      <c r="E7" s="70"/>
       <c r="F7" s="66">
         <v>2</v>
       </c>
@@ -4499,7 +4499,7 @@
       <c r="I7" s="67">
         <v>10.41</v>
       </c>
-      <c r="J7" s="68"/>
+      <c r="J7" s="69"/>
       <c r="K7" s="64">
         <v>3</v>
       </c>
@@ -4526,7 +4526,7 @@
       <c r="D8" s="51">
         <v>7.86</v>
       </c>
-      <c r="E8" s="78"/>
+      <c r="E8" s="70"/>
       <c r="F8" s="64">
         <v>2</v>
       </c>
@@ -4539,7 +4539,7 @@
       <c r="I8" s="65">
         <v>9</v>
       </c>
-      <c r="J8" s="68"/>
+      <c r="J8" s="69"/>
       <c r="K8" s="66">
         <v>3</v>
       </c>
@@ -4566,7 +4566,7 @@
       <c r="D9" s="51">
         <v>8.89</v>
       </c>
-      <c r="E9" s="78"/>
+      <c r="E9" s="70"/>
       <c r="F9" s="66">
         <v>2</v>
       </c>
@@ -4579,7 +4579,7 @@
       <c r="I9" s="67">
         <v>6.96</v>
       </c>
-      <c r="J9" s="68"/>
+      <c r="J9" s="69"/>
       <c r="K9" s="64">
         <v>3</v>
       </c>
@@ -4606,7 +4606,7 @@
       <c r="D10" s="51">
         <v>1.52</v>
       </c>
-      <c r="E10" s="78"/>
+      <c r="E10" s="70"/>
       <c r="F10" s="64">
         <v>2</v>
       </c>
@@ -4619,7 +4619,7 @@
       <c r="I10" s="65">
         <v>5.79</v>
       </c>
-      <c r="J10" s="68"/>
+      <c r="J10" s="69"/>
       <c r="K10" s="66">
         <v>3</v>
       </c>
@@ -4646,7 +4646,7 @@
       <c r="D11" s="51">
         <v>9.84</v>
       </c>
-      <c r="E11" s="78"/>
+      <c r="E11" s="70"/>
       <c r="F11" s="66">
         <v>2</v>
       </c>
@@ -4659,7 +4659,7 @@
       <c r="I11" s="67">
         <v>1.2</v>
       </c>
-      <c r="J11" s="68"/>
+      <c r="J11" s="69"/>
       <c r="K11" s="64">
         <v>3</v>
       </c>
@@ -4686,7 +4686,7 @@
       <c r="D12" s="51">
         <v>3.78</v>
       </c>
-      <c r="E12" s="78"/>
+      <c r="E12" s="70"/>
       <c r="F12" s="64">
         <v>2</v>
       </c>
@@ -4699,7 +4699,7 @@
       <c r="I12" s="65">
         <v>3.96</v>
       </c>
-      <c r="J12" s="68"/>
+      <c r="J12" s="69"/>
       <c r="K12" s="66">
         <v>3</v>
       </c>
@@ -4726,7 +4726,7 @@
       <c r="D13" s="51">
         <v>1.95</v>
       </c>
-      <c r="E13" s="78"/>
+      <c r="E13" s="70"/>
       <c r="F13" s="66">
         <v>2</v>
       </c>
@@ -4739,7 +4739,7 @@
       <c r="I13" s="67">
         <v>1.75</v>
       </c>
-      <c r="J13" s="68"/>
+      <c r="J13" s="69"/>
       <c r="K13" s="64">
         <v>3</v>
       </c>
@@ -4766,7 +4766,7 @@
       <c r="D14" s="51">
         <v>1.2</v>
       </c>
-      <c r="E14" s="78"/>
+      <c r="E14" s="70"/>
       <c r="F14" s="64">
         <v>2</v>
       </c>
@@ -4779,7 +4779,7 @@
       <c r="I14" s="65">
         <v>4.1500000000000004</v>
       </c>
-      <c r="J14" s="68"/>
+      <c r="J14" s="69"/>
       <c r="K14" s="66">
         <v>3</v>
       </c>
@@ -4807,7 +4807,7 @@
       <c r="D15" s="51">
         <v>12.5</v>
       </c>
-      <c r="E15" s="78"/>
+      <c r="E15" s="70"/>
       <c r="F15" s="66">
         <v>2</v>
       </c>
@@ -4820,7 +4820,7 @@
       <c r="I15" s="67">
         <v>5.56</v>
       </c>
-      <c r="J15" s="68"/>
+      <c r="J15" s="69"/>
       <c r="K15" s="64">
         <v>3</v>
       </c>
@@ -4847,7 +4847,7 @@
       <c r="D16" s="51">
         <v>4.08</v>
       </c>
-      <c r="E16" s="78"/>
+      <c r="E16" s="70"/>
       <c r="F16" s="64">
         <v>2</v>
       </c>
@@ -4860,7 +4860,7 @@
       <c r="I16" s="65">
         <v>15.79</v>
       </c>
-      <c r="J16" s="68"/>
+      <c r="J16" s="69"/>
       <c r="K16" s="66">
         <v>3</v>
       </c>
@@ -4887,7 +4887,7 @@
       <c r="D17" s="51">
         <v>12.1</v>
       </c>
-      <c r="E17" s="78"/>
+      <c r="E17" s="70"/>
       <c r="F17" s="66">
         <v>2</v>
       </c>
@@ -4900,7 +4900,7 @@
       <c r="I17" s="67">
         <v>1.76</v>
       </c>
-      <c r="J17" s="68"/>
+      <c r="J17" s="69"/>
       <c r="K17" s="64">
         <v>3</v>
       </c>
@@ -4928,7 +4928,7 @@
         <f>0.42+1.98</f>
         <v>2.4</v>
       </c>
-      <c r="E18" s="78"/>
+      <c r="E18" s="70"/>
       <c r="F18" s="64">
         <v>2</v>
       </c>
@@ -4941,7 +4941,7 @@
       <c r="I18" s="65">
         <v>7.48</v>
       </c>
-      <c r="J18" s="68"/>
+      <c r="J18" s="69"/>
       <c r="K18" s="66">
         <v>3</v>
       </c>
@@ -4968,7 +4968,7 @@
       <c r="D19" s="51">
         <v>21.81</v>
       </c>
-      <c r="E19" s="78"/>
+      <c r="E19" s="70"/>
       <c r="F19" s="66">
         <v>2</v>
       </c>
@@ -4981,7 +4981,7 @@
       <c r="I19" s="67">
         <v>1.88</v>
       </c>
-      <c r="J19" s="68"/>
+      <c r="J19" s="69"/>
       <c r="K19" s="64">
         <v>3</v>
       </c>
@@ -5008,7 +5008,7 @@
       <c r="D20" s="51">
         <v>1.59</v>
       </c>
-      <c r="E20" s="78"/>
+      <c r="E20" s="70"/>
       <c r="F20" s="64">
         <v>2</v>
       </c>
@@ -5021,7 +5021,7 @@
       <c r="I20" s="65">
         <v>12.78</v>
       </c>
-      <c r="J20" s="68"/>
+      <c r="J20" s="69"/>
       <c r="K20" s="66">
         <v>3</v>
       </c>
@@ -5048,7 +5048,7 @@
       <c r="D21" s="51">
         <v>2.4</v>
       </c>
-      <c r="E21" s="78"/>
+      <c r="E21" s="70"/>
       <c r="F21" s="66">
         <v>2</v>
       </c>
@@ -5061,7 +5061,7 @@
       <c r="I21" s="67">
         <v>5.38</v>
       </c>
-      <c r="J21" s="68"/>
+      <c r="J21" s="69"/>
       <c r="K21" s="64">
         <v>3</v>
       </c>
@@ -5088,7 +5088,7 @@
       <c r="D22" s="51">
         <v>4.53</v>
       </c>
-      <c r="E22" s="78"/>
+      <c r="E22" s="70"/>
       <c r="F22" s="64">
         <v>2</v>
       </c>
@@ -5101,7 +5101,7 @@
       <c r="I22" s="65">
         <v>1.36</v>
       </c>
-      <c r="J22" s="68"/>
+      <c r="J22" s="69"/>
       <c r="L22" s="59" t="s">
         <v>71</v>
       </c>
@@ -5126,7 +5126,7 @@
       <c r="D23" s="51">
         <v>10.92</v>
       </c>
-      <c r="E23" s="78"/>
+      <c r="E23" s="70"/>
       <c r="F23" s="66">
         <v>2</v>
       </c>
@@ -5139,11 +5139,11 @@
       <c r="I23" s="67">
         <v>8.0399999999999991</v>
       </c>
-      <c r="J23" s="68"/>
-      <c r="K23" s="68"/>
-      <c r="L23" s="68"/>
-      <c r="M23" s="68"/>
-      <c r="N23" s="68"/>
+      <c r="J23" s="69"/>
+      <c r="K23" s="69"/>
+      <c r="L23" s="69"/>
+      <c r="M23" s="69"/>
+      <c r="N23" s="69"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="56">
@@ -5158,7 +5158,7 @@
       <c r="D24" s="51">
         <v>2.6</v>
       </c>
-      <c r="E24" s="78"/>
+      <c r="E24" s="70"/>
       <c r="F24" s="64">
         <v>2</v>
       </c>
@@ -5171,11 +5171,11 @@
       <c r="I24" s="65">
         <v>4.5199999999999996</v>
       </c>
-      <c r="J24" s="68"/>
-      <c r="K24" s="68"/>
-      <c r="L24" s="68"/>
-      <c r="M24" s="68"/>
-      <c r="N24" s="68"/>
+      <c r="J24" s="69"/>
+      <c r="K24" s="69"/>
+      <c r="L24" s="69"/>
+      <c r="M24" s="69"/>
+      <c r="N24" s="69"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="56">
@@ -5190,7 +5190,7 @@
       <c r="D25" s="51">
         <v>1.77</v>
       </c>
-      <c r="E25" s="78"/>
+      <c r="E25" s="70"/>
       <c r="F25" s="66">
         <v>2</v>
       </c>
@@ -5203,11 +5203,11 @@
       <c r="I25" s="67">
         <v>6.51</v>
       </c>
-      <c r="J25" s="68"/>
-      <c r="K25" s="68"/>
-      <c r="L25" s="68"/>
-      <c r="M25" s="68"/>
-      <c r="N25" s="68"/>
+      <c r="J25" s="69"/>
+      <c r="K25" s="69"/>
+      <c r="L25" s="69"/>
+      <c r="M25" s="69"/>
+      <c r="N25" s="69"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="56">
@@ -5222,7 +5222,7 @@
       <c r="D26" s="51">
         <v>4.3</v>
       </c>
-      <c r="E26" s="78"/>
+      <c r="E26" s="70"/>
       <c r="F26" s="64">
         <v>2</v>
       </c>
@@ -5235,11 +5235,11 @@
       <c r="I26" s="65">
         <v>2.72</v>
       </c>
-      <c r="J26" s="68"/>
-      <c r="K26" s="68"/>
-      <c r="L26" s="68"/>
-      <c r="M26" s="68"/>
-      <c r="N26" s="68"/>
+      <c r="J26" s="69"/>
+      <c r="K26" s="69"/>
+      <c r="L26" s="69"/>
+      <c r="M26" s="69"/>
+      <c r="N26" s="69"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="56"/>
@@ -5253,7 +5253,7 @@
         <f>SUM(D6:D26)</f>
         <v>128.70000000000002</v>
       </c>
-      <c r="E27" s="78"/>
+      <c r="E27" s="70"/>
       <c r="G27" s="59" t="s">
         <v>71</v>
       </c>
@@ -5264,23 +5264,23 @@
         <f>SUM(I6:I26)</f>
         <v>121.62</v>
       </c>
-      <c r="J27" s="68"/>
-      <c r="K27" s="68"/>
-      <c r="L27" s="68"/>
-      <c r="M27" s="68"/>
-      <c r="N27" s="68"/>
+      <c r="J27" s="69"/>
+      <c r="K27" s="69"/>
+      <c r="L27" s="69"/>
+      <c r="M27" s="69"/>
+      <c r="N27" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="B2:J2"/>
+    <mergeCell ref="B3:J3"/>
     <mergeCell ref="A4:N4"/>
     <mergeCell ref="J5:J27"/>
     <mergeCell ref="E5:E27"/>
     <mergeCell ref="K23:N27"/>
     <mergeCell ref="K3:L3"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="B2:J2"/>
-    <mergeCell ref="B3:J3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -5292,7 +5292,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30.5546875" style="24" customWidth="1"/>
@@ -5300,7 +5300,7 @@
     <col min="3" max="16384" width="8.88671875" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="28" t="s">
         <v>8</v>
       </c>
@@ -5309,7 +5309,7 @@
       <c r="D1" s="23"/>
       <c r="E1" s="15"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>65</v>
       </c>
@@ -5326,7 +5326,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="36" x14ac:dyDescent="0.35">
       <c r="A3" s="25" t="s">
         <v>51</v>
       </c>
@@ -5341,8 +5341,12 @@
         <f>Таблица13[[#This Row],[ПГП]]+Таблица13[[#This Row],[ВПГП]]</f>
         <v>41.32</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G3" s="13" t="str">
+        <f>LEFT(Таблица13[[#This Row],[Помещения]], 4)</f>
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="26" t="s">
         <v>64</v>
       </c>
@@ -5357,8 +5361,12 @@
         <f>Таблица13[[#This Row],[ПГП]]+Таблица13[[#This Row],[ВПГП]]</f>
         <v>24.56</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="G4" s="13" t="str">
+        <f>LEFT(Таблица13[[#This Row],[Помещения]], 4)</f>
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="36" x14ac:dyDescent="0.35">
       <c r="A5" s="25" t="s">
         <v>49</v>
       </c>
@@ -5373,8 +5381,12 @@
         <f>Таблица13[[#This Row],[ПГП]]+Таблица13[[#This Row],[ВПГП]]</f>
         <v>11.96</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="G5" s="13" t="str">
+        <f>LEFT(Таблица13[[#This Row],[Помещения]], 4)</f>
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="36" x14ac:dyDescent="0.35">
       <c r="A6" s="25" t="s">
         <v>13</v>
       </c>
@@ -5389,8 +5401,12 @@
         <f>Таблица13[[#This Row],[ПГП]]+Таблица13[[#This Row],[ВПГП]]</f>
         <v>6.44</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="G6" s="13" t="str">
+        <f>LEFT(Таблица13[[#This Row],[Помещения]], 4)</f>
+        <v>1.10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="36" x14ac:dyDescent="0.35">
       <c r="A7" s="25" t="s">
         <v>34</v>
       </c>
@@ -5405,8 +5421,12 @@
         <f>Таблица13[[#This Row],[ПГП]]+Таблица13[[#This Row],[ВПГП]]</f>
         <v>8.24</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="72" x14ac:dyDescent="0.35">
+      <c r="G7" s="13" t="str">
+        <f>LEFT(Таблица13[[#This Row],[Помещения]], 4)</f>
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="72" x14ac:dyDescent="0.35">
       <c r="A8" s="25" t="s">
         <v>80</v>
       </c>
@@ -5421,8 +5441,12 @@
         <f>Таблица13[[#This Row],[ПГП]]+Таблица13[[#This Row],[ВПГП]]</f>
         <v>12.52</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G8" s="13" t="str">
+        <f>LEFT(Таблица13[[#This Row],[Помещения]], 4)</f>
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="25" t="s">
         <v>10</v>
       </c>
@@ -5437,8 +5461,12 @@
         <f>Таблица13[[#This Row],[ПГП]]+Таблица13[[#This Row],[ВПГП]]</f>
         <v>25.8</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="G9" s="13" t="str">
+        <f>LEFT(Таблица13[[#This Row],[Помещения]], 4)</f>
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="36" x14ac:dyDescent="0.35">
       <c r="A10" s="25" t="s">
         <v>12</v>
       </c>
@@ -5453,8 +5481,12 @@
         <f>Таблица13[[#This Row],[ПГП]]+Таблица13[[#This Row],[ВПГП]]</f>
         <v>28</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G10" s="13" t="str">
+        <f>LEFT(Таблица13[[#This Row],[Помещения]], 4)</f>
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="25" t="s">
         <v>50</v>
       </c>
@@ -5471,8 +5503,12 @@
         <f>Таблица13[[#This Row],[ПГП]]+Таблица13[[#This Row],[ВПГП]]</f>
         <v>11.35</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="G11" s="13" t="str">
+        <f>LEFT(Таблица13[[#This Row],[Помещения]], 4)</f>
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="36" x14ac:dyDescent="0.35">
       <c r="A12" s="25" t="s">
         <v>21</v>
       </c>
@@ -5487,8 +5523,12 @@
         <f>Таблица13[[#This Row],[ПГП]]+Таблица13[[#This Row],[ВПГП]]</f>
         <v>24.76</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="G12" s="13" t="str">
+        <f>LEFT(Таблица13[[#This Row],[Помещения]], 4)</f>
+        <v>1.30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="36" x14ac:dyDescent="0.35">
       <c r="A13" s="25" t="s">
         <v>22</v>
       </c>
@@ -5503,8 +5543,12 @@
         <f>Таблица13[[#This Row],[ПГП]]+Таблица13[[#This Row],[ВПГП]]</f>
         <v>13.6</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G13" s="13" t="str">
+        <f>LEFT(Таблица13[[#This Row],[Помещения]], 4)</f>
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="25" t="s">
         <v>52</v>
       </c>
@@ -5519,8 +5563,12 @@
         <f>Таблица13[[#This Row],[ПГП]]+Таблица13[[#This Row],[ВПГП]]</f>
         <v>42.36</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G14" s="13" t="str">
+        <f>LEFT(Таблица13[[#This Row],[Помещения]], 4)</f>
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="25" t="s">
         <v>54</v>
       </c>
@@ -5535,8 +5583,12 @@
         <f>Таблица13[[#This Row],[ПГП]]+Таблица13[[#This Row],[ВПГП]]</f>
         <v>17.84</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="G15" s="13" t="str">
+        <f>LEFT(Таблица13[[#This Row],[Помещения]], 4)</f>
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="36" x14ac:dyDescent="0.35">
       <c r="A16" s="25" t="s">
         <v>47</v>
       </c>
@@ -5551,8 +5603,12 @@
         <f>Таблица13[[#This Row],[ПГП]]+Таблица13[[#This Row],[ВПГП]]</f>
         <v>94.68</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G16" s="13" t="str">
+        <f>LEFT(Таблица13[[#This Row],[Помещения]], 4)</f>
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="25" t="s">
         <v>55</v>
       </c>
@@ -5567,8 +5623,12 @@
         <f>Таблица13[[#This Row],[ПГП]]+Таблица13[[#This Row],[ВПГП]]</f>
         <v>17.440000000000001</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="G17" s="13" t="str">
+        <f>LEFT(Таблица13[[#This Row],[Помещения]], 4)</f>
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="36" x14ac:dyDescent="0.35">
       <c r="A18" s="26" t="s">
         <v>63</v>
       </c>
@@ -5583,8 +5643,12 @@
         <f>Таблица13[[#This Row],[ПГП]]+Таблица13[[#This Row],[ВПГП]]</f>
         <v>94.32</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="G18" s="13" t="str">
+        <f>LEFT(Таблица13[[#This Row],[Помещения]], 4)</f>
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="36" x14ac:dyDescent="0.35">
       <c r="A19" s="25" t="s">
         <v>53</v>
       </c>
@@ -5601,8 +5665,12 @@
         <f>Таблица13[[#This Row],[ПГП]]+Таблица13[[#This Row],[ВПГП]]</f>
         <v>42.589999999999996</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G19" s="13" t="str">
+        <f>LEFT(Таблица13[[#This Row],[Помещения]], 4)</f>
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="47" t="s">
         <v>71</v>
       </c>
@@ -5633,7 +5701,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30.5546875" style="24" customWidth="1"/>
@@ -5644,7 +5712,7 @@
     <col min="6" max="16384" width="8.88671875" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="28" t="s">
         <v>8</v>
       </c>
@@ -5653,7 +5721,7 @@
       <c r="D1" s="23"/>
       <c r="E1" s="15"/>
     </row>
-    <row r="2" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="36" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>65</v>
       </c>
@@ -5670,7 +5738,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="36" x14ac:dyDescent="0.35">
       <c r="A3" s="25" t="s">
         <v>14</v>
       </c>
@@ -5685,8 +5753,12 @@
         <f>Таблица134[[#This Row],[ПГП]]+Таблица134[[#This Row],[АС влаго]]</f>
         <v>23.92</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="G3" s="13" t="str">
+        <f>LEFT(Таблица134[[#This Row],[Помещения]], 4)</f>
+        <v>2.03</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="36" x14ac:dyDescent="0.35">
       <c r="A4" s="25" t="s">
         <v>32</v>
       </c>
@@ -5703,8 +5775,12 @@
         <f>Таблица134[[#This Row],[ПГП]]+Таблица134[[#This Row],[АС влаго]]</f>
         <v>12.879999999999999</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G4" s="13" t="str">
+        <f>LEFT(Таблица134[[#This Row],[Помещения]], 4)</f>
+        <v>2.04</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="25" t="s">
         <v>33</v>
       </c>
@@ -5719,8 +5795,12 @@
         <f>Таблица134[[#This Row],[ПГП]]+Таблица134[[#This Row],[АС влаго]]</f>
         <v>14.96</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="G5" s="13" t="str">
+        <f>LEFT(Таблица134[[#This Row],[Помещения]], 4)</f>
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="36" x14ac:dyDescent="0.35">
       <c r="A6" s="25" t="s">
         <v>18</v>
       </c>
@@ -5735,8 +5815,12 @@
         <f>Таблица134[[#This Row],[ПГП]]+Таблица134[[#This Row],[АС влаго]]</f>
         <v>37.64</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="G6" s="13" t="str">
+        <f>LEFT(Таблица134[[#This Row],[Помещения]], 4)</f>
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="36" x14ac:dyDescent="0.35">
       <c r="A7" s="25" t="s">
         <v>79</v>
       </c>
@@ -5751,8 +5835,12 @@
         <f>Таблица134[[#This Row],[ПГП]]+Таблица134[[#This Row],[АС влаго]]</f>
         <v>40.270000000000003</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G7" s="13" t="str">
+        <f>LEFT(Таблица134[[#This Row],[Помещения]], 4)</f>
+        <v>2.13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="25" t="s">
         <v>78</v>
       </c>
@@ -5767,8 +5855,12 @@
         <f>Таблица134[[#This Row],[ПГП]]+Таблица134[[#This Row],[АС влаго]]</f>
         <v>47.9</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G8" s="13" t="str">
+        <f>LEFT(Таблица134[[#This Row],[Помещения]], 4)</f>
+        <v>2.14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="25" t="s">
         <v>19</v>
       </c>
@@ -5783,8 +5875,12 @@
         <f>Таблица134[[#This Row],[ПГП]]+Таблица134[[#This Row],[АС влаго]]</f>
         <v>37.4</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="54" x14ac:dyDescent="0.35">
+      <c r="G9" s="13" t="str">
+        <f>LEFT(Таблица134[[#This Row],[Помещения]], 4)</f>
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="54" x14ac:dyDescent="0.35">
       <c r="A10" s="25" t="s">
         <v>74</v>
       </c>
@@ -5799,8 +5895,12 @@
         <f>Таблица134[[#This Row],[ПГП]]+Таблица134[[#This Row],[АС влаго]]</f>
         <v>14.26</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G10" s="13" t="str">
+        <f>LEFT(Таблица134[[#This Row],[Помещения]], 4)</f>
+        <v>2.21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="25" t="s">
         <v>75</v>
       </c>
@@ -5815,8 +5915,12 @@
         <f>Таблица134[[#This Row],[ПГП]]+Таблица134[[#This Row],[АС влаго]]</f>
         <v>30.56</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G11" s="13" t="str">
+        <f>LEFT(Таблица134[[#This Row],[Помещения]], 4)</f>
+        <v>2.24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="25" t="s">
         <v>76</v>
       </c>
@@ -5831,8 +5935,12 @@
         <f>Таблица134[[#This Row],[ПГП]]+Таблица134[[#This Row],[АС влаго]]</f>
         <v>30.56</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="G12" s="13" t="str">
+        <f>LEFT(Таблица134[[#This Row],[Помещения]], 4)</f>
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="36" x14ac:dyDescent="0.35">
       <c r="A13" s="25" t="s">
         <v>24</v>
       </c>
@@ -5847,8 +5955,12 @@
         <f>Таблица134[[#This Row],[ПГП]]+Таблица134[[#This Row],[АС влаго]]</f>
         <v>13.6</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G13" s="13" t="str">
+        <f>LEFT(Таблица134[[#This Row],[Помещения]], 4)</f>
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="25" t="s">
         <v>61</v>
       </c>
@@ -5865,8 +5977,12 @@
         <f>Таблица134[[#This Row],[ПГП]]+Таблица134[[#This Row],[АС влаго]]</f>
         <v>27.84</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="G14" s="13" t="str">
+        <f>LEFT(Таблица134[[#This Row],[Помещения]], 4)</f>
+        <v>2.36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="36" x14ac:dyDescent="0.35">
       <c r="A15" s="25" t="s">
         <v>57</v>
       </c>
@@ -5881,8 +5997,12 @@
         <f>Таблица134[[#This Row],[ПГП]]+Таблица134[[#This Row],[АС влаго]]</f>
         <v>94.36</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G15" s="13" t="str">
+        <f>LEFT(Таблица134[[#This Row],[Помещения]], 4)</f>
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="25" t="s">
         <v>62</v>
       </c>
@@ -5897,8 +6017,12 @@
         <f>Таблица134[[#This Row],[ПГП]]+Таблица134[[#This Row],[АС влаго]]</f>
         <v>17.440000000000001</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="G16" s="13" t="str">
+        <f>LEFT(Таблица134[[#This Row],[Помещения]], 4)</f>
+        <v>2.43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="36" x14ac:dyDescent="0.35">
       <c r="A17" s="25" t="s">
         <v>58</v>
       </c>
@@ -5913,8 +6037,12 @@
         <f>Таблица134[[#This Row],[ПГП]]+Таблица134[[#This Row],[АС влаго]]</f>
         <v>94.36</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="G17" s="13" t="str">
+        <f>LEFT(Таблица134[[#This Row],[Помещения]], 4)</f>
+        <v>2.46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="36" x14ac:dyDescent="0.35">
       <c r="A18" s="25" t="s">
         <v>77</v>
       </c>
@@ -5929,8 +6057,12 @@
         <f>Таблица134[[#This Row],[ПГП]]+Таблица134[[#This Row],[АС влаго]]</f>
         <v>8.32</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G18" s="13" t="str">
+        <f>LEFT(Таблица134[[#This Row],[Помещения]], 4)</f>
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="25" t="s">
         <v>35</v>
       </c>
@@ -5945,8 +6077,12 @@
         <f>Таблица134[[#This Row],[ПГП]]+Таблица134[[#This Row],[АС влаго]]</f>
         <v>5.12</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="G19" s="13" t="str">
+        <f>LEFT(Таблица134[[#This Row],[Помещения]], 4)</f>
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="36" x14ac:dyDescent="0.35">
       <c r="A20" s="25" t="s">
         <v>56</v>
       </c>
@@ -5961,8 +6097,12 @@
         <f>Таблица134[[#This Row],[ПГП]]+Таблица134[[#This Row],[АС влаго]]</f>
         <v>13.04</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="G20" s="13" t="str">
+        <f>LEFT(Таблица134[[#This Row],[Помещения]], 4)</f>
+        <v>2.50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="36" x14ac:dyDescent="0.35">
       <c r="A21" s="25" t="s">
         <v>60</v>
       </c>
@@ -5977,8 +6117,12 @@
         <f>Таблица134[[#This Row],[ПГП]]+Таблица134[[#This Row],[АС влаго]]</f>
         <v>20.72</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G21" s="13" t="str">
+        <f>LEFT(Таблица134[[#This Row],[Помещения]], 4)</f>
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="25" t="s">
         <v>30</v>
       </c>
@@ -5993,8 +6137,12 @@
         <f>Таблица134[[#This Row],[ПГП]]+Таблица134[[#This Row],[АС влаго]]</f>
         <v>6.8</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G22" s="13" t="str">
+        <f>LEFT(Таблица134[[#This Row],[Помещения]], 4)</f>
+        <v>2.56</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="47" t="s">
         <v>71</v>
       </c>
@@ -6025,7 +6173,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="35.77734375" style="24" customWidth="1"/>
@@ -6033,7 +6181,7 @@
     <col min="3" max="16384" width="8.88671875" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="28" t="s">
         <v>8</v>
       </c>
@@ -6042,7 +6190,7 @@
       <c r="D1" s="23"/>
       <c r="E1" s="15"/>
     </row>
-    <row r="2" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="36" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>65</v>
       </c>
@@ -6059,7 +6207,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="25" t="s">
         <v>73</v>
       </c>
@@ -6076,8 +6224,12 @@
         <f>Таблица1345[[#This Row],[ПГП]]+Таблица1345[[#This Row],[АС влаго]]</f>
         <v>19.86</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G3" s="13" t="str">
+        <f>LEFT(Таблица1345[[#This Row],[Помещения]], 4)</f>
+        <v>3.06</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="25" t="s">
         <v>27</v>
       </c>
@@ -6092,8 +6244,12 @@
         <f>Таблица1345[[#This Row],[ПГП]]+Таблица1345[[#This Row],[АС влаго]]</f>
         <v>25.76</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="54" x14ac:dyDescent="0.35">
+      <c r="G4" s="13" t="str">
+        <f>LEFT(Таблица1345[[#This Row],[Помещения]], 4)</f>
+        <v>3.10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="54" x14ac:dyDescent="0.35">
       <c r="A5" s="25" t="s">
         <v>70</v>
       </c>
@@ -6110,8 +6266,12 @@
         <f>Таблица1345[[#This Row],[ПГП]]+Таблица1345[[#This Row],[АС влаго]]</f>
         <v>25.439999999999998</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G5" s="13" t="str">
+        <f>LEFT(Таблица1345[[#This Row],[Помещения]], 4)</f>
+        <v>3.12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="25" t="s">
         <v>25</v>
       </c>
@@ -6126,8 +6286,12 @@
         <f>Таблица1345[[#This Row],[ПГП]]+Таблица1345[[#This Row],[АС влаго]]</f>
         <v>2.4</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="G6" s="13" t="str">
+        <f>LEFT(Таблица1345[[#This Row],[Помещения]], 4)</f>
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="36" x14ac:dyDescent="0.35">
       <c r="A7" s="25" t="s">
         <v>28</v>
       </c>
@@ -6142,8 +6306,12 @@
         <f>Таблица1345[[#This Row],[ПГП]]+Таблица1345[[#This Row],[АС влаго]]</f>
         <v>13.6</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G7" s="13" t="str">
+        <f>LEFT(Таблица1345[[#This Row],[Помещения]], 4)</f>
+        <v>3.21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="25" t="s">
         <v>39</v>
       </c>
@@ -6158,8 +6326,12 @@
         <f>Таблица1345[[#This Row],[ПГП]]+Таблица1345[[#This Row],[АС влаго]]</f>
         <v>26.05</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G8" s="13" t="str">
+        <f>LEFT(Таблица1345[[#This Row],[Помещения]], 4)</f>
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="25" t="s">
         <v>40</v>
       </c>
@@ -6174,8 +6346,12 @@
         <f>Таблица1345[[#This Row],[ПГП]]+Таблица1345[[#This Row],[АС влаго]]</f>
         <v>19.04</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G9" s="13" t="str">
+        <f>LEFT(Таблица1345[[#This Row],[Помещения]], 4)</f>
+        <v>3.24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="25" t="s">
         <v>38</v>
       </c>
@@ -6190,8 +6366,12 @@
         <f>Таблица1345[[#This Row],[ПГП]]+Таблица1345[[#This Row],[АС влаго]]</f>
         <v>19.920000000000002</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G10" s="13" t="str">
+        <f>LEFT(Таблица1345[[#This Row],[Помещения]], 4)</f>
+        <v>3.26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="25" t="s">
         <v>46</v>
       </c>
@@ -6206,8 +6386,12 @@
         <f>Таблица1345[[#This Row],[ПГП]]+Таблица1345[[#This Row],[АС влаго]]</f>
         <v>86.68</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G11" s="13" t="str">
+        <f>LEFT(Таблица1345[[#This Row],[Помещения]], 4)</f>
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="25" t="s">
         <v>37</v>
       </c>
@@ -6222,8 +6406,12 @@
         <f>Таблица1345[[#This Row],[ПГП]]+Таблица1345[[#This Row],[АС влаго]]</f>
         <v>31.06</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G12" s="13" t="str">
+        <f>LEFT(Таблица1345[[#This Row],[Помещения]], 4)</f>
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="25" t="s">
         <v>36</v>
       </c>
@@ -6238,8 +6426,12 @@
         <f>Таблица1345[[#This Row],[ПГП]]+Таблица1345[[#This Row],[АС влаго]]</f>
         <v>19.399999999999999</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G13" s="13" t="str">
+        <f>LEFT(Таблица1345[[#This Row],[Помещения]], 4)</f>
+        <v>3.31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="25" t="s">
         <v>45</v>
       </c>
@@ -6254,8 +6446,12 @@
         <f>Таблица1345[[#This Row],[ПГП]]+Таблица1345[[#This Row],[АС влаго]]</f>
         <v>86.08</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" ht="90" x14ac:dyDescent="0.35">
+      <c r="G14" s="13" t="str">
+        <f>LEFT(Таблица1345[[#This Row],[Помещения]], 4)</f>
+        <v>3.32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="90" x14ac:dyDescent="0.35">
       <c r="A15" s="25" t="s">
         <v>43</v>
       </c>
@@ -6270,8 +6466,12 @@
         <f>Таблица1345[[#This Row],[ПГП]]+Таблица1345[[#This Row],[АС влаго]]</f>
         <v>8.7200000000000006</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" ht="90" x14ac:dyDescent="0.35">
+      <c r="G15" s="13" t="str">
+        <f>LEFT(Таблица1345[[#This Row],[Помещения]], 4)</f>
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="90" x14ac:dyDescent="0.35">
       <c r="A16" s="25" t="s">
         <v>42</v>
       </c>
@@ -6286,8 +6486,12 @@
         <f>Таблица1345[[#This Row],[ПГП]]+Таблица1345[[#This Row],[АС влаго]]</f>
         <v>3.8</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="G16" s="13" t="str">
+        <f>LEFT(Таблица1345[[#This Row],[Помещения]], 4)</f>
+        <v>3.35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="36" x14ac:dyDescent="0.35">
       <c r="A17" s="25" t="s">
         <v>41</v>
       </c>
@@ -6304,8 +6508,12 @@
         <f>Таблица1345[[#This Row],[ПГП]]+Таблица1345[[#This Row],[АС влаго]]</f>
         <v>9.64</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G17" s="13" t="str">
+        <f>LEFT(Таблица1345[[#This Row],[Помещения]], 4)</f>
+        <v>3.40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="25" t="s">
         <v>44</v>
       </c>
@@ -6320,8 +6528,12 @@
         <f>Таблица1345[[#This Row],[ПГП]]+Таблица1345[[#This Row],[АС влаго]]</f>
         <v>6.78</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G18" s="13" t="str">
+        <f>LEFT(Таблица1345[[#This Row],[Помещения]], 4)</f>
+        <v>3.42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="47" t="s">
         <v>71</v>
       </c>
